--- a/docs/Checklist 2/Cronograma final.xlsx
+++ b/docs/Checklist 2/Cronograma final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Desenvolvimento de sistemas\Repositorio\SIFCQA-da-FMX\docs\Checklist 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB45C87-BC4D-443B-AB4A-9D660E0B1685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523CD257-955D-4744-9FEF-55380EB208CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{60F8E2A4-1620-4B96-BB34-CCCC53EF35ED}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t>Tarefa</t>
   </si>
@@ -79,12 +79,6 @@
   </si>
   <si>
     <t>S14</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>S16</t>
   </si>
   <si>
     <t>X</t>
@@ -585,22 +579,18 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
     </row>
     <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -619,12 +609,12 @@
     </row>
     <row r="3" spans="1:17" ht="45" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -642,12 +632,12 @@
     </row>
     <row r="4" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -665,12 +655,12 @@
     </row>
     <row r="5" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -688,13 +678,13 @@
     </row>
     <row r="6" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -711,16 +701,16 @@
     </row>
     <row r="7" spans="1:17" ht="60" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -736,17 +726,17 @@
     </row>
     <row r="8" spans="1:17" ht="45" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -761,7 +751,7 @@
     </row>
     <row r="9" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -769,10 +759,10 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -786,7 +776,7 @@
     </row>
     <row r="10" spans="1:17" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -796,7 +786,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -809,7 +799,7 @@
     </row>
     <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -818,10 +808,10 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -834,7 +824,7 @@
     </row>
     <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -844,10 +834,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -859,7 +849,7 @@
     </row>
     <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -870,10 +860,10 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -884,7 +874,7 @@
     </row>
     <row r="14" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -896,10 +886,10 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -909,7 +899,7 @@
     </row>
     <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -922,10 +912,10 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -934,7 +924,7 @@
     </row>
     <row r="16" spans="1:17" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -948,7 +938,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -957,7 +947,7 @@
     </row>
     <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -971,18 +961,20 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
     <row r="18" spans="1:17" ht="30" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -998,14 +990,10 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:Q18">
